--- a/education_surveys/022_international_exchange_program_impact_evaluation--education_surveys.xlsx
+++ b/education_surveys/022_international_exchange_program_impact_evaluation--education_surveys.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange_participant_info</t>
+          <t>exchange_participant_info_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Exchange Participant Information</t>
+          <t>Exchange Participant Info 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>exchange_outcomes</t>
+          <t>exchange_outcomes_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>program_outcomes</t>
+          <t>program_outcomes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Program Outcomes</t>
+          <t>Program Outcomes 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>participant_outcomes</t>
+          <t>participant_outcomes_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Participant Outcomes</t>
+          <t>Participant Outcomes 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>participant_program_outcomes</t>
+          <t>participant_program_outcomes_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Participant Program Outcomes</t>
+          <t>Participant Program Outcomes 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>exchange_program_outcomes</t>
+          <t>exchange_program_outcomes_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
